--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/LF/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/LF/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingRTandDIM\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6207B1F4-1348-4609-BE24-6E4615112B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6872C82F-7C63-42FA-9E60-1E1365554FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,8 +171,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -492,34 +493,34 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>24.111111111111111</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>4.5878765361669318</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>13.555555555555555</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>3.1369217041197843</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>34.388888888888886</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>4.1741599287893951</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>24.018518518518519</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>3.0736835985829081</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>10.462962962962962</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>3.259364476416144</v>
       </c>
     </row>
@@ -527,34 +528,34 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>19.625</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>3.2596012026013246</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>11</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>1.4880476182856899</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>33.9375</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>4.2210146038262275</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>21.520833333333332</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>1.9240283055700917</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>10.520833333333332</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>2.2911796019199349</v>
       </c>
     </row>
@@ -562,34 +563,34 @@
       <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>17.916666666666668</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2.2229859798628175</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>12.666666666666666</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>1.8348478592697199</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>31.25</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>4.2632147494584416</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>20.611111111111111</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>1.3851059593108819</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>7.9444444444444455</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>1.8698385749300077</v>
       </c>
     </row>
@@ -597,39 +598,49 @@
       <c r="A6" t="s">
         <v>31</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>18.899999999999999</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>1.8506755523321747</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>12.8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>3.2132538026119239</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>32.5</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>4.7169905660283016</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>21.400000000000002</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>2.2687490434647515</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>8.6</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>1.5211472278806206</v>
       </c>
     </row>
